--- a/etf_holdings/2026-10-06_errors.xlsx
+++ b/etf_holdings/2026-10-06_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,24 +441,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:16:06</t>
+          <t>2026-10-06 19:15:25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00991A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>00980A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-10-06 19:16:26</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00980A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/etf_holdings/2026-10-06_errors.xlsx
+++ b/etf_holdings/2026-10-06_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,49 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-06 19:15:25</t>
+          <t>2026-10-06 23:21:09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00991A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>00980A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-10-06 19:16:26</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00980A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00993A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
